--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
-  <si>
-    <t>Statement: workoutSessionExercisesSchema – validate the array of exercises in a session. Minimum one entry.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="176">
+  <si>
+    <t>Statement: workoutSessionExercisesSchema – Validates an array of workout session exercise entries using Zod safeParse. Returns { success: true, data } when the array contains at least one entry and every entry satisfies its field constraints. Returns { success: false, error } when the array is empty or any entry violates a constraint. Array constraints: minimum length 1. Per-entry constraints: exerciseId is required (at least 1 character after trimming, not whitespace-only; surrounding whitespace trimmed). sets is required and must be an integer in the range 0–6 inclusive. reps is required and must be an integer in the range 0–30 inclusive. weight is required and must be a number in the range 0.0–500.0 inclusive.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: Array&lt;{ exerciseId: string, sets: number, reps: number, weight: number }&gt;</t>
+    <t>Input: Array&lt;WorkoutSessionExerciseInput { exerciseId: string, sets: number, reps: number, weight: number }&gt;</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>length ≥ 1 | 0 ≤ sets ≤ 6 | 0 ≤ reps ≤ 30 | 0.0 ≤ weight ≤ 500.0</t>
+    <t>Input is passed directly to workoutSessionExercisesSchema.safeParse(). Array must contain at least 1 entry. Per entry: exerciseId is required, at least 1 character after trim, not whitespace-only, surrounding whitespace trimmed. sets: required, integer, 0 ≤ sets ≤ 6. reps: required, integer, 0 ≤ reps ≤ 30. weight: required, number, 0.0 ≤ weight ≤ 500.0.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: WorkoutSessionExerciseInput[], error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data is an array of entries with exerciseId trimmed. On failure: error.issues[0].path contains the index of the offending entry and/or the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,61 +64,52 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Single exercise</t>
-  </si>
-  <si>
-    <t>Length=1</t>
-  </si>
-  <si>
-    <t>Multiple exercises</t>
-  </si>
-  <si>
-    <t>Length &gt; 1</t>
-  </si>
-  <si>
-    <t>Empty array</t>
-  </si>
-  <si>
-    <t>Length=0</t>
-  </si>
-  <si>
-    <t>ExerciseId presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>ExerciseId value</t>
-  </si>
-  <si>
-    <t>Non-whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace only</t>
-  </si>
-  <si>
-    <t>Sets type</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>Reps type</t>
-  </si>
-  <si>
-    <t>Weight type</t>
-  </si>
-  <si>
-    <t>ExerciseId whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace</t>
+    <t>Array length</t>
+  </si>
+  <si>
+    <t>Array with 1 entry (all fields valid) → success: true, parsed data has length 1</t>
+  </si>
+  <si>
+    <t>Array with 2 entries (all fields valid) → success: true, parsed data has length 2</t>
+  </si>
+  <si>
+    <t>Empty array [] → success: false</t>
+  </si>
+  <si>
+    <t>exerciseId presence</t>
+  </si>
+  <si>
+    <t>Entry with exerciseId field absent → success: false, error path contains "exerciseId"</t>
+  </si>
+  <si>
+    <t>exerciseId value</t>
+  </si>
+  <si>
+    <t>Entry with exerciseId: "   " (whitespace-only) → success: false, error path contains "exerciseId"</t>
+  </si>
+  <si>
+    <t>sets type</t>
+  </si>
+  <si>
+    <t>Entry with sets: "invalid" (string instead of number) → success: false, error path contains "sets"</t>
+  </si>
+  <si>
+    <t>reps type</t>
+  </si>
+  <si>
+    <t>Entry with reps: "invalid" (string instead of number) → success: false, error path contains "reps"</t>
+  </si>
+  <si>
+    <t>weight type</t>
+  </si>
+  <si>
+    <t>Entry with weight: "invalid" (string instead of number) → success: false, error path contains "weight"</t>
+  </si>
+  <si>
+    <t>exerciseId whitespace</t>
+  </si>
+  <si>
+    <t>Entry with exerciseId: "  exercise-123  " (surrounding whitespace) → success: true, parsed exerciseId is "exercise-123"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -139,10 +130,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Single valid exercise</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>array containing one entry with all fields valid: exerciseId "exercise-123", sets 3, reps 10, weight 80.5</t>
+  </si>
+  <si>
+    <t>success: true, parsed data has length 1 and matches the input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -151,13 +142,16 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Multiple valid exercises</t>
+    <t>array containing two entries, both with all fields valid, second entry has exerciseId "exercise-456"</t>
+  </si>
+  <si>
+    <t>success: true, parsed data has length 2, second entry exerciseId is "exercise-456"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>[] (empty array)</t>
+    <t>empty array []</t>
   </si>
   <si>
     <t>success: false</t>
@@ -166,37 +160,55 @@
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing exerciseId field</t>
+    <t>array with one entry where exerciseId field is absent: { sets: 3, reps: 10, weight: 80.5 }</t>
+  </si>
+  <si>
+    <t>success: false, error path contains index 0 and "exerciseId"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>exerciseId="   "</t>
+    <t>array with one entry where exerciseId: "   " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "exerciseId"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>sets="invalid" (String)</t>
+    <t>array with one entry where sets: "invalid" (string)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "sets"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>reps="invalid" (String)</t>
+    <t>array with one entry where reps: "invalid" (string)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "reps"</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>weight="invalid" (String)</t>
+    <t>array with one entry where weight: "invalid" (string)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "weight"</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>exerciseId="  exercise-123  "</t>
+    <t>array with one entry where exerciseId: "  exercise-123  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed exerciseId is "exercise-123"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -205,178 +217,229 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Sets range</t>
-  </si>
-  <si>
-    <t>-1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0 (At Min)</t>
-  </si>
-  <si>
-    <t>1 (Above Min)</t>
-  </si>
-  <si>
-    <t>5 (Below Max)</t>
-  </si>
-  <si>
-    <t>6 (At Max)</t>
-  </si>
-  <si>
-    <t>7 (Above Max)</t>
-  </si>
-  <si>
-    <t>Reps range</t>
-  </si>
-  <si>
-    <t>29 (Below Max)</t>
-  </si>
-  <si>
-    <t>30 (At Max)</t>
-  </si>
-  <si>
-    <t>31 (Above Max)</t>
-  </si>
-  <si>
-    <t>Weight range</t>
-  </si>
-  <si>
-    <t>-0.1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0.0 (At Min)</t>
-  </si>
-  <si>
-    <t>0.1 (Above Min)</t>
-  </si>
-  <si>
-    <t>499.9 (Below Max)</t>
-  </si>
-  <si>
-    <t>500.0 (At Max)</t>
-  </si>
-  <si>
-    <t>500.1 (Above Max)</t>
-  </si>
-  <si>
-    <t>1 char padded</t>
+    <t>sets range</t>
+  </si>
+  <si>
+    <t>sets: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>sets: 0 (min): at minimum → success: true, parsed sets is 0</t>
+  </si>
+  <si>
+    <t>sets: 1 (min + 1): above minimum → success: true, parsed sets is 1</t>
+  </si>
+  <si>
+    <t>sets: 5 (max - 1): below maximum → success: true, parsed sets is 5</t>
+  </si>
+  <si>
+    <t>sets: 6 (max): at maximum → success: true, parsed sets is 6</t>
+  </si>
+  <si>
+    <t>sets: 7 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>reps range</t>
+  </si>
+  <si>
+    <t>reps: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>reps: 0 (min): at minimum → success: true, parsed reps is 0</t>
+  </si>
+  <si>
+    <t>reps: 1 (min + 1): above minimum → success: true, parsed reps is 1</t>
+  </si>
+  <si>
+    <t>reps: 29 (max - 1): below maximum → success: true, parsed reps is 29</t>
+  </si>
+  <si>
+    <t>reps: 30 (max): at maximum → success: true, parsed reps is 30</t>
+  </si>
+  <si>
+    <t>reps: 31 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>weight range</t>
+  </si>
+  <si>
+    <t>weight: -0.1 (min - 0.1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>weight: 0.0 (min): at minimum → success: true, parsed weight is 0</t>
+  </si>
+  <si>
+    <t>weight: 0.1 (min + 0.1): above minimum → success: true, parsed weight is 0.1</t>
+  </si>
+  <si>
+    <t>weight: 499.9 (max - 0.1): below maximum → success: true, parsed weight is 499.9</t>
+  </si>
+  <si>
+    <t>weight: 500.0 (max): at maximum → success: true, parsed weight is 500</t>
+  </si>
+  <si>
+    <t>weight: 500.1 (max + 0.1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>exerciseId whitespace + trim</t>
+  </si>
+  <si>
+    <t>exerciseId: " E " (1 real character after trim, at minimum) → success: true, parsed exerciseId is "E"</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Sets -1</t>
-  </si>
-  <si>
-    <t>sets=-1</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 0</t>
-  </si>
-  <si>
-    <t>sets=0</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 1</t>
-  </si>
-  <si>
-    <t>sets=1</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 5</t>
-  </si>
-  <si>
-    <t>sets=5</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 6</t>
-  </si>
-  <si>
-    <t>sets=6</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 7</t>
-  </si>
-  <si>
-    <t>sets=7</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps -1</t>
-  </si>
-  <si>
-    <t>reps=-1</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 0</t>
-  </si>
-  <si>
-    <t>reps=0</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 1</t>
-  </si>
-  <si>
-    <t>reps=1</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 29</t>
-  </si>
-  <si>
-    <t>reps=29</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 30</t>
-  </si>
-  <si>
-    <t>reps=30</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 31</t>
-  </si>
-  <si>
-    <t>reps=31</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight -0.1</t>
-  </si>
-  <si>
-    <t>weight=-0.1</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 0</t>
-  </si>
-  <si>
-    <t>weight=0</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 0.1</t>
-  </si>
-  <si>
-    <t>weight=0.1</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 499.9</t>
-  </si>
-  <si>
-    <t>weight=499.9</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 500</t>
-  </si>
-  <si>
-    <t>weight=500</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 500.1</t>
-  </si>
-  <si>
-    <t>weight=500.1</t>
-  </si>
-  <si>
-    <t>BVA-4 ExerciseId padded</t>
-  </si>
-  <si>
-    <t>exerciseId=" E "</t>
+    <t>BVA-1  (sets=-1)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: -1</t>
+  </si>
+  <si>
+    <t>BVA-2  (sets=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 0</t>
+  </si>
+  <si>
+    <t>BVA-3  (sets=1)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 1</t>
+  </si>
+  <si>
+    <t>BVA-4  (sets=5)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 5</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 5</t>
+  </si>
+  <si>
+    <t>BVA-5  (sets=6)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 6</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 6</t>
+  </si>
+  <si>
+    <t>BVA-6  (sets=7)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 7</t>
+  </si>
+  <si>
+    <t>BVA-7  (reps=-1)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: -1</t>
+  </si>
+  <si>
+    <t>BVA-8  (reps=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 0</t>
+  </si>
+  <si>
+    <t>BVA-9  (reps=1)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 1</t>
+  </si>
+  <si>
+    <t>BVA-10 (reps=29)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 29</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 29</t>
+  </si>
+  <si>
+    <t>BVA-11 (reps=30)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 30</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 30</t>
+  </si>
+  <si>
+    <t>BVA-12 (reps=31)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 31</t>
+  </si>
+  <si>
+    <t>BVA-13 (wt=-0.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: -0.1</t>
+  </si>
+  <si>
+    <t>BVA-14 (wt=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 0</t>
+  </si>
+  <si>
+    <t>BVA-15 (wt=0.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 0.1</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 0.1</t>
+  </si>
+  <si>
+    <t>BVA-16 (wt=499.9)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 499.9</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 499.9</t>
+  </si>
+  <si>
+    <t>BVA-17 (wt=500)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 500</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 500</t>
+  </si>
+  <si>
+    <t>BVA-18 (wt=500.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 500.1</t>
+  </si>
+  <si>
+    <t>BVA-19 (pad→1)</t>
+  </si>
+  <si>
+    <t>array with one entry where exerciseId: " E " (1 real character after trim)</t>
+  </si>
+  <si>
+    <t>success: true, parsed exerciseId is "E"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -385,100 +448,61 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Single valid exercise row</t>
-  </si>
-  <si>
-    <t>Multiple valid exercise rows</t>
-  </si>
-  <si>
-    <t>Empty exercises array []</t>
-  </si>
-  <si>
-    <t>Exercise entry missing id</t>
-  </si>
-  <si>
-    <t>exerciseId="   " (Whitespace)</t>
-  </si>
-  <si>
-    <t>sets="invalid" (Type error)</t>
-  </si>
-  <si>
-    <t>reps="invalid" (Type error)</t>
-  </si>
-  <si>
-    <t>weight="invalid" (Type error)</t>
-  </si>
-  <si>
-    <t>ExerciseId with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>sets=-1 (Below range)</t>
-  </si>
-  <si>
-    <t>sets=0 (At boundary)</t>
-  </si>
-  <si>
-    <t>sets=1 (Inside range)</t>
-  </si>
-  <si>
-    <t>sets=5 (Inside range)</t>
-  </si>
-  <si>
-    <t>sets=6 (At boundary)</t>
-  </si>
-  <si>
-    <t>sets=7 (Above range)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>reps=-1 (Below range)</t>
-  </si>
-  <si>
-    <t>reps=0 (At boundary)</t>
-  </si>
-  <si>
-    <t>reps=1 (Inside range)</t>
-  </si>
-  <si>
-    <t>reps=29 (Inside range)</t>
-  </si>
-  <si>
-    <t>reps=30 (At boundary)</t>
-  </si>
-  <si>
-    <t>reps=31 (Above range)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>weight=-0.1 (Below range)</t>
-  </si>
-  <si>
-    <t>weight=0 (At boundary)</t>
-  </si>
-  <si>
-    <t>weight=0.1 (Inside range)</t>
-  </si>
-  <si>
-    <t>weight=499.9 (Inside range)</t>
-  </si>
-  <si>
-    <t>weight=500 (At boundary)</t>
-  </si>
-  <si>
-    <t>weight=500.1 (Above range)</t>
-  </si>
-  <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>exerciseId 1 char padded with whitespace</t>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
   </si>
   <si>
     <t>Testing</t>
@@ -511,7 +535,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-02/WSM-03</t>
+    <t>SCHEMA-10</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1077,10 +1101,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -1091,13 +1115,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,13 +1129,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,13 +1143,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,13 +1157,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1147,13 +1171,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,13 +1185,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1175,10 +1199,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1</v>
@@ -1204,19 +1228,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1224,16 +1248,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1241,16 +1265,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1258,16 +1282,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1275,16 +1299,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1292,16 +1316,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1315,10 +1339,10 @@
         <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1326,16 +1350,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1343,16 +1367,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1360,16 +1384,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1390,13 +1414,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1404,208 +1428,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>1</v>
+      <c r="A17" s="1">
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
+      <c r="A19" s="1">
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1628,19 +1652,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1648,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1665,16 +1689,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1682,16 +1706,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1699,16 +1723,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1716,16 +1740,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,16 +1757,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1750,16 +1774,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1767,16 +1791,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1784,16 +1808,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1801,16 +1825,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1818,16 +1842,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1835,16 +1859,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1852,16 +1876,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1869,16 +1893,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1886,16 +1910,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1903,16 +1927,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1920,16 +1944,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1937,16 +1961,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1954,16 +1978,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1987,22 +2011,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2010,19 +2034,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2030,19 +2054,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,19 +2074,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2070,19 +2094,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2090,19 +2114,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2116,13 +2140,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,19 +2154,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,19 +2174,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,19 +2194,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,16 +2217,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2213,16 +2237,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2233,16 +2257,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2253,16 +2277,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2273,16 +2297,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,16 +2317,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2313,16 +2337,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2333,16 +2357,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2353,16 +2377,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2373,16 +2397,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2393,16 +2417,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2413,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2433,16 +2457,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2453,16 +2477,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,16 +2497,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2493,16 +2517,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2513,16 +2537,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2533,16 +2557,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,16 +2577,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2590,16 +2614,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2607,39 +2631,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B3" s="1">
         <v>28</v>
@@ -2654,19 +2678,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
@@ -535,7 +535,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-10</t>
+    <t>SCHEMA-12</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesSchema-bbt-form.xlsx
@@ -535,7 +535,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-12</t>
+    <t>SCHEMA-13</t>
   </si>
   <si>
     <t>n/a</t>
